--- a/technology_surveys/015_software_freedom_principles_survey--technology_surveys.xlsx
+++ b/technology_surveys/015_software_freedom_principles_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_is_distributed_without_any_copyright'}</t>
+          <t>free_and_open-source_software_is_distributed_without_any_copyright</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software is distributed without any copyright'}</t>
+          <t>Free and open-source software is distributed without any copyright</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_has_no_cost,_or_can_be_distributed_at_no_cost'}</t>
+          <t>free_and_open-source_software_has_no_cost,_or_can_be_distributed_at_no_cost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software has no cost, or can be distributed at no cost'}</t>
+          <t>Free and open-source software has no cost, or can be distributed at no cost</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_is_distributed_under_open-source_licenses_that_give_users_the_freedom_to_study,_modify_and_redistribute_it'}</t>
+          <t>free_and_open-source_software_is_distributed_under_open-source_licenses_that_give_users_the_freedom_to_study,_modify_and_redistribute_it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software is distributed under open-source licenses that give users the freedom to study, modify and redistribute it'}</t>
+          <t>Free and open-source software is distributed under open-source licenses that give users the freedom to study, modify and redistribute it</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_is_used_for_social_good,_such_as_in_education,_science,_or_healthcare'}</t>
+          <t>free_and_open-source_software_is_used_for_social_good,_such_as_in_education,_science,_or_healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software is used for social good, such as in education, science, or healthcare'}</t>
+          <t>Free and open-source software is used for social good, such as in education, science, or healthcare</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_use_the_software_for_any_purpose'}</t>
+          <t>users_have_the_freedom_to_use_the_software_for_any_purpose</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to use the software for any purpose'}</t>
+          <t>Users have the freedom to use the software for any purpose</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_study_the_software_and_understand_how_it_works'}</t>
+          <t>users_have_the_freedom_to_study_the_software_and_understand_how_it_works</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to study the software and understand how it works'}</t>
+          <t>Users have the freedom to study the software and understand how it works</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_modify_and_distribute_copies_of_the_software'}</t>
+          <t>users_have_the_freedom_to_modify_and_distribute_copies_of_the_software</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to modify and distribute copies of the software'}</t>
+          <t>Users have the freedom to modify and distribute copies of the software</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_modify_the_software_and_distribute_derivative_works_based_on_it'}</t>
+          <t>users_have_the_freedom_to_modify_the_software_and_distribute_derivative_works_based_on_it</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to modify the software and distribute derivative works based on it'}</t>
+          <t>Users have the freedom to modify the software and distribute derivative works based on it</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_make_and_sell_a_modified_version_of_the_software'}</t>
+          <t>users_have_the_freedom_to_make_and_sell_a_modified_version_of_the_software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to make and sell a modified version of the software'}</t>
+          <t>Users have the freedom to make and sell a modified version of the software</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'users_have_the_freedom_to_distribute_copies_of_the_software_and_charge_for_it'}</t>
+          <t>users_have_the_freedom_to_distribute_copies_of_the_software_and_charge_for_it</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Users have the freedom to distribute copies of the software and charge for it'}</t>
+          <t>Users have the freedom to distribute copies of the software and charge for it</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'contributing_patches'}</t>
+          <t>contributing_patches</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Contributing patches'}</t>
+          <t>Contributing patches</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'contributing_code'}</t>
+          <t>contributing_code</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Contributing code'}</t>
+          <t>Contributing code</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'contributing_documentation'}</t>
+          <t>contributing_documentation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Contributing documentation'}</t>
+          <t>Contributing documentation</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'contributing_to_community_projects'}</t>
+          <t>contributing_to_community_projects</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Contributing to community projects'}</t>
+          <t>Contributing to community projects</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_community_decision-making'}</t>
+          <t>participating_in_community_decision-making</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in community decision-making'}</t>
+          <t>Participating in community decision-making</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'advocating_for_free_and_open-source_software'}</t>
+          <t>advocating_for_free_and_open-source_software</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Advocating for free and open-source software'}</t>
+          <t>Advocating for free and open-source software</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_online_forums'}</t>
+          <t>participating_in_online_forums</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in online forums'}</t>
+          <t>Participating in online forums</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_local_meetups'}</t>
+          <t>participating_in_local_meetups</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in local meetups'}</t>
+          <t>Participating in local meetups</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_social_media_groups'}</t>
+          <t>participating_in_social_media_groups</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in social media groups'}</t>
+          <t>Participating in social media groups</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_community_events'}</t>
+          <t>participating_in_community_events</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in community events'}</t>
+          <t>Participating in community events</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'participating_in_hackathons'}</t>
+          <t>participating_in_hackathons</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Participating in hackathons'}</t>
+          <t>Participating in hackathons</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_development_is_important_for_the_future_of_technology'}</t>
+          <t>free_and_open-source_software_development_is_important_for_the_future_of_technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software development is important for the future of technology'}</t>
+          <t>Free and open-source software development is important for the future of technology</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'the_freedom_to_use,_modify_and_distribute_software_is_essential_for_innovation'}</t>
+          <t>the_freedom_to_use,_modify_and_distribute_software_is_essential_for_innovation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'The freedom to use, modify and distribute software is essential for innovation'}</t>
+          <t>The freedom to use, modify and distribute software is essential for innovation</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_is_more_secure_than_proprietary_software'}</t>
+          <t>free_and_open-source_software_is_more_secure_than_proprietary_software</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software is more secure than proprietary software'}</t>
+          <t>Free and open-source software is more secure than proprietary software</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_development_is_essential_for_social_good'}</t>
+          <t>free_and_open-source_software_development_is_essential_for_social_good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software development is essential for social good'}</t>
+          <t>Free and open-source software development is essential for social good</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_development_is_more_efficient_than_proprietary_software_development'}</t>
+          <t>free_and_open-source_software_development_is_more_efficient_than_proprietary_software_development</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software development is more efficient than proprietary software development'}</t>
+          <t>Free and open-source software development is more efficient than proprietary software development</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'free_and_open-source_software_development_is_more_reliable_than_proprietary_software_development'}</t>
+          <t>free_and_open-source_software_development_is_more_reliable_than_proprietary_software_development</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Free and open-source software development is more reliable than proprietary software development'}</t>
+          <t>Free and open-source software development is more reliable than proprietary software development</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'more_cost-effective'}</t>
+          <t>more_cost-effective</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'More cost-effective'}</t>
+          <t>More cost-effective</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'more_reliable'}</t>
+          <t>more_reliable</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'More reliable'}</t>
+          <t>More reliable</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'more_efficient'}</t>
+          <t>more_efficient</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'More efficient'}</t>
+          <t>More efficient</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'more_secure'}</t>
+          <t>more_secure</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'More secure'}</t>
+          <t>More secure</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'more_flexible'}</t>
+          <t>more_flexible</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'More flexible'}</t>
+          <t>More flexible</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'more_innovative'}</t>
+          <t>more_innovative</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'More innovative'}</t>
+          <t>More innovative</t>
         </is>
       </c>
     </row>
